--- a/deliverables/qc_gap_analysis/tracker/CoQ_Master_Register_2026-09-18.xlsx
+++ b/deliverables/qc_gap_analysis/tracker/CoQ_Master_Register_2026-09-18.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr"/>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -11270,7 +11270,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="N88" s="3" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -16373,7 +16373,7 @@
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N126" s="3" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -19288,7 +19288,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N143" s="3" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
@@ -21198,7 +21198,7 @@
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N156" s="3" t="inlineStr">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N163" s="3" t="inlineStr">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N164" s="3" t="inlineStr">
@@ -22433,7 +22433,7 @@
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="N165" s="3" t="inlineStr">
@@ -23159,7 +23159,7 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
@@ -23278,7 +23278,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N172" s="3" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -23717,7 +23717,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -26623,7 +26623,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -27163,7 +27163,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -27433,7 +27433,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -27568,7 +27568,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -30156,7 +30156,7 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr"/>
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -32383,7 +32383,7 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -32514,7 +32514,7 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr"/>
@@ -33287,7 +33287,7 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>GorillaGlue</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr">
@@ -34311,7 +34311,7 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>JellyDonutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
@@ -35017,7 +35017,7 @@
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N90" s="3" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr">
@@ -35255,7 +35255,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>GrapePie</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -35853,7 +35853,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -36131,7 +36131,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -40162,7 +40162,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -40857,7 +40857,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -42938,7 +42938,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -43077,7 +43077,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>Cup Junky</t>
+          <t>Cap Junky</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -43482,7 +43482,7 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>FatBastard</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -44582,7 +44582,7 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grapes And Cream</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -44987,7 +44987,7 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
@@ -45539,7 +45539,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>Permanent Market</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -45948,7 +45948,7 @@
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -46083,7 +46083,7 @@
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="N78" s="3" t="inlineStr">
@@ -46222,7 +46222,7 @@
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr">
